--- a/output/pdf_financials_xlsx/QTWO.xlsx
+++ b/output/pdf_financials_xlsx/QTWO.xlsx
@@ -1318,34 +1318,34 @@
         <v>-0.113184</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.186294</v>
+        <v>-0.186294</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.63316</v>
+        <v>-2.63316</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.706707</v>
+        <v>-0.706707</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.754205</v>
+        <v>-0.754205</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.51354</v>
+        <v>-0.51354</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.138531</v>
+        <v>-0.138531</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.159579</v>
+        <v>-0.159579</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.366454</v>
+        <v>-0.366454</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.522762</v>
+        <v>-1.522762</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.051837</v>
+        <v>-0.051837</v>
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
@@ -1358,16 +1358,16 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.898841</v>
+        <v>-1.898841</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.196324</v>
+        <v>-0.196324</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>5.715847</v>
+        <v>-5.183847</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>16.188518</v>
+        <v>-10.740518</v>
       </c>
     </row>
     <row r="17">
@@ -1626,34 +1626,34 @@
         <v>-0.113184</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.186294</v>
+        <v>-0.186294</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.63316</v>
+        <v>-2.63316</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.706707</v>
+        <v>-0.706707</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.754205</v>
+        <v>-0.754205</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.51354</v>
+        <v>-0.51354</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.138531</v>
+        <v>-0.138531</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.159579</v>
+        <v>-0.159579</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.366454</v>
+        <v>-0.366454</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.522762</v>
+        <v>-1.522762</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.051837</v>
+        <v>-0.051837</v>
       </c>
       <c r="M20" s="1" t="inlineStr">
         <is>
@@ -1666,16 +1666,16 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>1.898841</v>
+        <v>-1.898841</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.196324</v>
+        <v>-0.196324</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>5.449847</v>
+        <v>-5.449847</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>13.464518</v>
+        <v>-13.464518</v>
       </c>
     </row>
     <row r="21">
@@ -1812,34 +1812,34 @@
         <v>-0.113184</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.186294</v>
+        <v>-0.186294</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.63316</v>
+        <v>-2.63316</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.706707</v>
+        <v>-0.706707</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.754205</v>
+        <v>-0.754205</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.51354</v>
+        <v>-0.51354</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.138531</v>
+        <v>-0.138531</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.159579</v>
+        <v>-0.159579</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.366454</v>
+        <v>-0.366454</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.522762</v>
+        <v>-1.522762</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.051837</v>
+        <v>-0.051837</v>
       </c>
       <c r="M23" s="1" t="inlineStr">
         <is>
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.898841</v>
+        <v>-1.898841</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.196324</v>
+        <v>-0.196324</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>5.449847</v>
+        <v>-5.449847</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>13.464518</v>
+        <v>-13.464518</v>
       </c>
     </row>
     <row r="24">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>13.843291</v>
+        <v>-13.843291</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>47.471025</v>
+        <v>-47.471025</v>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>108.99694</v>
+        <v>-108.99694</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>168.306475</v>
+        <v>-168.306475</v>
       </c>
     </row>
     <row r="27">
@@ -2112,34 +2112,34 @@
         <v>-0.113184</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.186294</v>
+        <v>-0.186294</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.63316</v>
+        <v>-2.63316</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.706707</v>
+        <v>-0.706707</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.754205</v>
+        <v>-0.754205</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.51354</v>
+        <v>-0.51354</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.138531</v>
+        <v>-0.138531</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.159579</v>
+        <v>-0.159579</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.366454</v>
+        <v>-0.366454</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.522762</v>
+        <v>-1.522762</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.051837</v>
+        <v>-0.051837</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.898841</v>
+        <v>-1.898841</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.196324</v>
+        <v>-0.196324</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>5.715847</v>
+        <v>-5.183847</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>16.188518</v>
+        <v>-10.740518</v>
       </c>
     </row>
     <row r="28">
@@ -2236,34 +2236,34 @@
         <v>-0.113184</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.186294</v>
+        <v>-0.186294</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.63316</v>
+        <v>-2.63316</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.713139</v>
+        <v>-0.700275</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.760055</v>
+        <v>-0.748355</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.518313</v>
+        <v>-0.508767</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.142443</v>
+        <v>-0.134619</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.162709</v>
+        <v>-0.156449</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.368958</v>
+        <v>-0.36395</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.522762</v>
+        <v>-1.522762</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.051837</v>
+        <v>-0.051837</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2276,16 +2276,16 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.898841</v>
+        <v>-1.898841</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.196324</v>
+        <v>-0.196324</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>5.715847</v>
+        <v>-5.183847</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>16.188518</v>
+        <v>-10.740518</v>
       </c>
     </row>
     <row r="30">
@@ -2390,34 +2390,34 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="1" t="inlineStr">
         <is>
@@ -2430,16 +2430,16 @@
         </is>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>4.653728485034677</v>
+        <v>-5.131324284840969</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>16.82674102718977</v>
+        <v>-25.36190526378709</v>
       </c>
     </row>
     <row r="32">
@@ -8032,28 +8032,28 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.569925</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.263559</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.730093</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.203177</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.016181</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.05901</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.229828</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.006947</v>
       </c>
       <c r="K118" s="1" t="inlineStr">
         <is>
@@ -20445,7 +20445,11 @@
           <t>Interest in exploration properties and exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -28884,10 +28888,10 @@
         </is>
       </c>
       <c r="T198" s="5" t="n">
-        <v>5.449847</v>
+        <v>-5.449847</v>
       </c>
       <c r="U198" s="5" t="n">
-        <v>13.464518</v>
+        <v>-13.464518</v>
       </c>
     </row>
     <row r="199">
@@ -30668,13 +30672,13 @@
         </is>
       </c>
       <c r="R216" s="5" t="n">
-        <v>1.898841</v>
+        <v>-1.898841</v>
       </c>
       <c r="S216" s="5" t="n">
-        <v>0.196324</v>
+        <v>-0.196324</v>
       </c>
       <c r="T216" s="5" t="n">
-        <v>5.449847</v>
+        <v>-5.449847</v>
       </c>
       <c r="U216" t="inlineStr">
         <is>
@@ -32242,10 +32246,10 @@
         </is>
       </c>
       <c r="N232" s="5" t="n">
-        <v>1.522762</v>
+        <v>-1.522762</v>
       </c>
       <c r="O232" s="5" t="n">
-        <v>0.051837</v>
+        <v>-0.051837</v>
       </c>
       <c r="P232" t="inlineStr">
         <is>
@@ -32907,10 +32911,10 @@
         </is>
       </c>
       <c r="L239" s="5" t="n">
-        <v>0.159579</v>
+        <v>-0.159579</v>
       </c>
       <c r="M239" s="5" t="n">
-        <v>0.366454</v>
+        <v>-0.366454</v>
       </c>
       <c r="N239" t="inlineStr">
         <is>
@@ -33201,10 +33205,10 @@
         </is>
       </c>
       <c r="K242" s="5" t="n">
-        <v>0.138531</v>
+        <v>-0.138531</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>0.159579</v>
+        <v>-0.159579</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
@@ -33572,22 +33576,22 @@
         </is>
       </c>
       <c r="F246" s="5" t="n">
-        <v>0.186294</v>
+        <v>-0.186294</v>
       </c>
       <c r="G246" s="5" t="n">
-        <v>2.63316</v>
+        <v>-2.63316</v>
       </c>
       <c r="H246" s="5" t="n">
-        <v>0.706707</v>
+        <v>-0.706707</v>
       </c>
       <c r="I246" s="5" t="n">
-        <v>0.754205</v>
+        <v>-0.754205</v>
       </c>
       <c r="J246" s="5" t="n">
-        <v>0.51354</v>
+        <v>-0.51354</v>
       </c>
       <c r="K246" s="5" t="n">
-        <v>0.138531</v>
+        <v>-0.138531</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/QTWO.xlsx
+++ b/output/pdf_financials_xlsx/QTWO.xlsx
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.0009840000000000001</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000899</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000897</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007531</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00045</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1113,13 +1113,13 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.45336</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.19941</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.47928</v>
       </c>
     </row>
     <row r="13">
@@ -2109,19 +2109,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.113184</v>
+        <v>-0.114168</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.186294</v>
+        <v>-0.185395</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.63316</v>
+        <v>-2.632263</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.706707</v>
+        <v>-0.699176</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.754205</v>
+        <v>-0.753755</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.51354</v>
@@ -2155,13 +2155,13 @@
         <v>-1.898841</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.196324</v>
+        <v>-0.649684</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-5.183847</v>
+        <v>-4.984437</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-10.740518</v>
+        <v>-10.261238</v>
       </c>
     </row>
     <row r="28">
@@ -2233,19 +2233,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.113184</v>
+        <v>-0.114168</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.186294</v>
+        <v>-0.185395</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.63316</v>
+        <v>-2.632263</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.700275</v>
+        <v>-0.692744</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.748355</v>
+        <v>-0.747905</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.508767</v>
@@ -2279,13 +2279,13 @@
         <v>-1.898841</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.196324</v>
+        <v>-0.649684</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-5.183847</v>
+        <v>-4.984437</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-10.740518</v>
+        <v>-10.261238</v>
       </c>
     </row>
     <row r="30">
@@ -2573,22 +2573,22 @@
         <v>0.004518</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.007129</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.014098</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.017163</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.010305</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.04148</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.946403</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>12.010842</v>
@@ -2697,22 +2697,22 @@
         <v>0.004518</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.007129</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.014098</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.017163</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.010305</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.04148</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.946403</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>12.010842</v>
@@ -3441,22 +3441,22 @@
         <v>0.008326999999999999</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.029604</v>
+        <v>0.022475</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.01742</v>
+        <v>0.003322</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.024161</v>
+        <v>0.006998</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.010305</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.037486</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.149129</v>
+        <v>0.202726</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.040172</v>
@@ -12444,7 +12444,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -28205,7 +28205,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -29591,7 +29591,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -29997,7 +29997,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -31603,7 +31603,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -32672,7 +32672,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -33961,7 +33961,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -34666,7 +34666,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -35264,7 +35264,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E263" s="5" t="n">
